--- a/notebooks/Ale/rf_model_quality_summary.xlsx
+++ b/notebooks/Ale/rf_model_quality_summary.xlsx
@@ -559,14 +559,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0619</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0649</v>
+        <v>0.0301</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -582,14 +582,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0788</v>
+        <v>-0.04</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0885</v>
+        <v>-0.0505</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.4266</v>
+        <v>0.5214</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.3645</v>
+        <v>0.434</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>0.2354</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>0.1101</v>
+      <c r="B8" s="8" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.0682</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>✅ Recomendado</t>
         </is>
       </c>
     </row>
@@ -685,46 +685,46 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.6914</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0.6999</v>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0.5599</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>✅ Recomendado</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>0.5142</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0.5316</v>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.4878</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.4639</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>❌ No usar</t>
         </is>
       </c>
     </row>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.7536</v>
+        <v>0.7923</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>0.6549</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.602</v>
+        <v>0.7157</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0.7068</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -852,18 +852,18 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.08749999999999999</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>0.1053</v>
+          <t>gd_bus</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.0426</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -875,14 +875,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0117</v>
+        <v>0.0516</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0256</v>
+        <v>0.0482</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.747</v>
+        <v>0.757</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.7396</v>
+        <v>0.6877</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.6433</v>
+        <v>0.6341</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.3186</v>
+        <v>0.4745</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -978,18 +978,18 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
+          <t>gd_bus_binary</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.573</v>
+        <v>0.5933</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.6276</v>
+        <v>0.5365</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1001,14 +1001,14 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.5703</v>
+        <v>0.5986</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5561</v>
+        <v>0.5606</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.7997</v>
+        <v>0.8098</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.7712</v>
+        <v>0.7805</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -1051,14 +1051,14 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.5617</v>
+        <v>0.5911</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.5909</v>
+        <v>0.5651</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1145,14 +1145,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>-0.2438</v>
+        <v>-0.5431</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-0.2647</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0019</v>
+        <v>-0.2215</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0021</v>
+        <v>-0.26</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1195,14 +1195,14 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-30.5146</v>
+        <v>-3.0207</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-10.1142</v>
+        <v>-3.0487</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1248,14 +1248,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.7378</v>
+        <v>0.7329</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.7562</v>
+        <v>0.7477</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1392,37 +1392,37 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>0.1455</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>0.1533</v>
+          <t>gd_bus</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.0172</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>❌ No usar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0048</v>
+        <v>0.0672</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.046</v>
+        <v>0.0351</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.5769</v>
+        <v>0.6281</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.5678</v>
+        <v>0.5631</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.5264</v>
+        <v>0.5068</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.2819</v>
+        <v>0.2835</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1518,14 +1518,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
+          <t>gd_bus_binary</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.5794</v>
+        <v>0.593</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -1541,18 +1541,18 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.5313</v>
+        <v>0.5278</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.7824</v>
+        <v>0.7271</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7147</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.6395</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5423</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.4633</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1685,37 +1685,37 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.09130000000000001</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.06950000000000001</v>
+          <t>gd_bus</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0.1257</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>❌ No usar</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0631</v>
+        <v>-0.0646</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0694</v>
+        <v>-0.0759</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1734,20 +1734,20 @@
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0.0731</v>
+      <c r="B7" s="9" t="n">
+        <v>0.157</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0487</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>❌ No usar</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
         </is>
       </c>
     </row>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0917</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.0426</v>
+        <v>-0.3747</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1811,41 +1811,41 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.7032</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0.6923</v>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0.6198</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>✅ Recomendado</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.54</v>
+        <v>0.5462</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5538</v>
+        <v>0.5366</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.139</v>
+        <v>0.2105</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1336</v>
+        <v>0.1629</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.345</v>
+        <v>0.16</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.2105</v>
+        <v>0</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1978,14 +1978,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.1313</v>
+        <v>0.194</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0677</v>
+        <v>0.0193</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2001,18 +2001,18 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0176</v>
+        <v>-0.0238</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0118</v>
+        <v>-0.0469</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.2576</v>
+        <v>0.2203</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.1527</v>
+        <v>0.1001</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>-0.019</v>
+        <v>0.0134</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.0394</v>
+        <v>-0.0119</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
+          <t>gd_bus_binary</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.8435</v>
+        <v>0.8405</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.8388</v>
+        <v>0.823</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -2127,18 +2127,18 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.5343</v>
+        <v>0.5324</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5379</v>
+        <v>0.5254</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4848</v>
+        <v>0.4941</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.4471</v>
+        <v>0.1709</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.0563</v>
+        <v>0.0485</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -2271,14 +2271,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>-0.044</v>
+        <v>0.0284</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-0.1178</v>
+        <v>0.0045</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2294,14 +2294,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-0.0229</v>
+        <v>0.004</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.6956</v>
+        <v>0.6327</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.6932</v>
+        <v>0.5753</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.4524</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.381</v>
+        <v>0.4115</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.26</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -2397,14 +2397,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
+          <t>gd_bus_binary</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.5972</v>
+        <v>0.6373</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.5734</v>
+        <v>0.6082</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -2420,18 +2420,18 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.5805</v>
+        <v>0.5695</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5566</v>
+        <v>0.5854</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2447,14 +2447,14 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.8056</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.798</v>
+        <v>0.7792</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -2469,15 +2469,15 @@
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>0.6143999999999999</v>
+      <c r="B15" s="6" t="n">
+        <v>0.468</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.5944</v>
+        <v>0.5046</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">

--- a/notebooks/Ale/rf_model_quality_summary.xlsx
+++ b/notebooks/Ale/rf_model_quality_summary.xlsx
@@ -566,7 +566,7 @@
         <v>0.0619</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0301</v>
+        <v>0.0142</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>-0.04</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0505</v>
+        <v>-0.0447</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         <v>0.5214</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.434</v>
+        <v>0.4368</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -634,8 +634,8 @@
       <c r="B8" s="8" t="n">
         <v>0.3858</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0.0682</v>
+      <c r="C8" s="9" t="n">
+        <v>0.1682</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>0.572</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.5599</v>
+        <v>0.5364</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>0.4878</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.4639</v>
+        <v>0.4751</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>0.7923</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.738</v>
+        <v>0.7764</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -761,11 +761,11 @@
         <v>0.7157</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.7068</v>
+        <v>0.7363</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -859,7 +859,7 @@
         <v>0.1079</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0426</v>
+        <v>0.0522</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>0.0516</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.0482</v>
+        <v>0.0304</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -905,11 +905,11 @@
         <v>0.757</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.6877</v>
+        <v>0.7662</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -928,7 +928,7 @@
         <v>0.6341</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.4745</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>0.5933</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.5365</v>
+        <v>0.569</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>0.5986</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5606</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>0.8098</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.7805</v>
+        <v>0.7603</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>0.5911</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.5651</v>
+        <v>0.5673</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1152,11 +1152,11 @@
         <v>-0.5431</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.4986</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1175,11 +1175,11 @@
         <v>-0.2215</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.26</v>
+        <v>-0.2177</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1198,7 +1198,7 @@
         <v>-3.0207</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-3.0487</v>
+        <v>-5.7961</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>0.7329</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.7477</v>
+        <v>0.7534</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1398,17 +1398,17 @@
       <c r="B5" s="6" t="n">
         <v>0.0564</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0.0172</v>
+      <c r="C5" s="9" t="n">
+        <v>0.1023</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>❌ No usar</t>
+          <t>theory</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
         <v>0.0672</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.0351</v>
+        <v>0.0598</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>0.6281</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.5631</v>
+        <v>0.6052</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1467,8 +1467,8 @@
       <c r="B8" s="8" t="n">
         <v>0.5068</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>0.2835</v>
+      <c r="C8" s="8" t="n">
+        <v>0.4397</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>0.6452</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.593</v>
+        <v>0.5601</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>0.5278</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.52</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
         <v>0.7271</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.7147</v>
+        <v>0.7315</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1594,7 +1594,7 @@
         <v>0.5423</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.4633</v>
+        <v>0.4802</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1691,8 +1691,8 @@
       <c r="B5" s="9" t="n">
         <v>0.1258</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>0.1257</v>
+      <c r="C5" s="6" t="n">
+        <v>-0.0008</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1715,11 +1715,11 @@
         <v>-0.0646</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0759</v>
+        <v>-0.0496</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1738,7 +1738,7 @@
         <v>0.157</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.0487</v>
+        <v>0.017</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>0.0917</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.3747</v>
+        <v>-0.0746</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1818,11 +1818,11 @@
         <v>0.628</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.6198</v>
+        <v>0.6435</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1841,7 +1841,7 @@
         <v>0.5462</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5366</v>
+        <v>0.519</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>0.2105</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1629</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>0.16</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>0.194</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0193</v>
+        <v>-0.0448</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>-0.0238</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-0.0469</v>
+        <v>-0.0421</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>0.2203</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.1001</v>
+        <v>0.1178</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>0.0134</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.0119</v>
+        <v>-0.0058</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>0.8405</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.823</v>
+        <v>0.8404</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>0.5324</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5254</v>
+        <v>0.5103</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>0.4941</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1709</v>
+        <v>0.4002</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -2180,11 +2180,11 @@
         <v>0.0485</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -2278,7 +2278,7 @@
         <v>0.0284</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0045</v>
+        <v>-0.0216</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -2301,11 +2301,11 @@
         <v>0.004</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.0109</v>
+        <v>-0.0144</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2324,7 +2324,7 @@
         <v>0.6327</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.5753</v>
+        <v>0.6086</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -2346,8 +2346,8 @@
       <c r="B8" s="8" t="n">
         <v>0.4115</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>0.26</v>
+      <c r="C8" s="8" t="n">
+        <v>0.3479</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -2403,17 +2403,17 @@
       <c r="B12" s="9" t="n">
         <v>0.6373</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>0.6082</v>
+      <c r="C12" s="8" t="n">
+        <v>0.6677</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
+          <t>theory</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>✅ Recomendado</t>
         </is>
       </c>
     </row>
@@ -2427,11 +2427,11 @@
         <v>0.5695</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.5854</v>
+        <v>0.5006</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2450,7 +2450,7 @@
         <v>0.8056</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.7792</v>
+        <v>0.7553</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -2472,17 +2472,17 @@
       <c r="B15" s="6" t="n">
         <v>0.468</v>
       </c>
-      <c r="C15" s="9" t="n">
-        <v>0.5046</v>
+      <c r="C15" s="6" t="n">
+        <v>0.4611</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>theory</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>❌ No usar</t>
         </is>
       </c>
     </row>
